--- a/artfynd/A 50718-2023 artfynd.xlsx
+++ b/artfynd/A 50718-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50718-2023 artfynd.xlsx
+++ b/artfynd/A 50718-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,6 +2015,2488 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114976462</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95110</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>676099</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6614534</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114976199</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90224</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>676142</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6614564</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114976226</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99815</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>676142</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6614564</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114978291</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104642</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>676056</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6614574</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114976338</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104642</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>676160</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6614538</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114977437</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95110</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>675968</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6614628</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114977198</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74600</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>676004</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6614613</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114976638</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90260</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>676086</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6614538</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114977093</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95110</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>675999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6614613</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114978278</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5162</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>676070</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6614606</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114978809</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104642</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>676159</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6614531</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114976365</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99815</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>676151</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6614510</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114977131</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95110</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>676012</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6614601</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114978754</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90224</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>676201</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6614620</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114978658</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90224</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>676170</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6614608</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114976157</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90660</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>676142</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6614564</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114978026</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90224</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>675976</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6614671</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114977763</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90278</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>675950</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6614674</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114977582</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90260</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>675957</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6614653</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114977364</v>
+      </c>
+      <c r="B34" t="n">
+        <v>94182</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>210</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>675967</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6614626</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114977300</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>675966</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6614654</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114976438</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99815</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>676121</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6614524</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114977540</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90540</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långkärret (Långkärret), Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>675957</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6614654</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114978933</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>676142</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6614564</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50718-2023 artfynd.xlsx
+++ b/artfynd/A 50718-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113279721</v>
+        <v>114976462</v>
       </c>
       <c r="B2" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676034</v>
+        <v>676099</v>
       </c>
       <c r="R2" t="n">
-        <v>6614554</v>
+        <v>6614533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,12 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,63 +761,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113279813</v>
+        <v>114977093</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676066</v>
+        <v>675999</v>
       </c>
       <c r="R3" t="n">
-        <v>6614544</v>
+        <v>6614613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,12 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,63 +859,58 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113279911</v>
+        <v>114977131</v>
       </c>
       <c r="B4" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676137</v>
+        <v>676011</v>
       </c>
       <c r="R4" t="n">
-        <v>6614516</v>
+        <v>6614602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,12 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,63 +957,58 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113279738</v>
+        <v>114977437</v>
       </c>
       <c r="B5" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långkärret, Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676034</v>
+        <v>675968</v>
       </c>
       <c r="R5" t="n">
-        <v>6614554</v>
+        <v>6614628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,27 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113279825</v>
+        <v>114977364</v>
       </c>
       <c r="B6" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,38 +1078,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676068</v>
+        <v>675967</v>
       </c>
       <c r="R6" t="n">
-        <v>6614544</v>
+        <v>6614626</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,63 +1153,58 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113316500</v>
+        <v>114977540</v>
       </c>
       <c r="B7" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676168</v>
+        <v>675957</v>
       </c>
       <c r="R7" t="n">
-        <v>6614617</v>
+        <v>6614653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,12 +1231,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,65 +1251,58 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113314815</v>
+        <v>114976638</v>
       </c>
       <c r="B8" t="n">
-        <v>90951</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långkärret, Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676034</v>
+        <v>676086</v>
       </c>
       <c r="R8" t="n">
-        <v>6614554</v>
+        <v>6614538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1329,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,70 +1343,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113314627</v>
+        <v>114977582</v>
       </c>
       <c r="B9" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676172</v>
+        <v>675957</v>
       </c>
       <c r="R9" t="n">
-        <v>6614601</v>
+        <v>6614652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,12 +1427,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,63 +1447,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113315786</v>
+        <v>113314815</v>
       </c>
       <c r="B10" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676169</v>
+        <v>676034</v>
       </c>
       <c r="R10" t="n">
-        <v>6614668</v>
+        <v>6614554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,12 +1527,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,6 +1541,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1605,15 +1560,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113316046</v>
+        <v>115531877</v>
       </c>
       <c r="B11" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,35 +1571,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676020</v>
+        <v>676148</v>
       </c>
       <c r="R11" t="n">
-        <v>6614565</v>
+        <v>6614492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,12 +1625,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,51 +1657,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113302450</v>
+        <v>113279721</v>
       </c>
       <c r="B12" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676114</v>
+        <v>676034</v>
       </c>
       <c r="R12" t="n">
-        <v>6614541</v>
+        <v>6614554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,12 +1723,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,54 +1755,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113591226</v>
+        <v>113279825</v>
       </c>
       <c r="B13" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676165</v>
+        <v>676068</v>
       </c>
       <c r="R13" t="n">
-        <v>6614551</v>
+        <v>6614544</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,12 +1821,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,63 +1841,58 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113591623</v>
+        <v>113279882</v>
       </c>
       <c r="B14" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676020</v>
+        <v>676107</v>
       </c>
       <c r="R14" t="n">
-        <v>6614604</v>
+        <v>6614511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,12 +1919,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,27 +1939,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114976157</v>
+        <v>114976408</v>
       </c>
       <c r="B15" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,35 +1962,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långkärret, Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676142</v>
+        <v>676141</v>
       </c>
       <c r="R15" t="n">
-        <v>6614564</v>
+        <v>6614508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,51 +2049,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114976638</v>
+        <v>114978933</v>
       </c>
       <c r="B16" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676086</v>
+        <v>676142</v>
       </c>
       <c r="R16" t="n">
-        <v>6614538</v>
+        <v>6614564</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,51 +2147,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114977582</v>
+        <v>114976157</v>
       </c>
       <c r="B17" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>675957</v>
+        <v>676142</v>
       </c>
       <c r="R17" t="n">
-        <v>6614652</v>
+        <v>6614564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,51 +2245,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114978809</v>
+        <v>113302450</v>
       </c>
       <c r="B18" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676159</v>
+        <v>676114</v>
       </c>
       <c r="R18" t="n">
-        <v>6614531</v>
+        <v>6614541</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,12 +2311,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,15 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114977131</v>
+        <v>113315786</v>
       </c>
       <c r="B19" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,35 +2354,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>676011</v>
+        <v>676169</v>
       </c>
       <c r="R19" t="n">
-        <v>6614602</v>
+        <v>6614668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,12 +2409,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,68 +2429,58 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114978278</v>
+        <v>113591226</v>
       </c>
       <c r="B20" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676070</v>
+        <v>676165</v>
       </c>
       <c r="R20" t="n">
-        <v>6614606</v>
+        <v>6614551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,12 +2507,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,51 +2539,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114977364</v>
+        <v>113591623</v>
       </c>
       <c r="B21" t="n">
-        <v>94275</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>675967</v>
+        <v>676020</v>
       </c>
       <c r="R21" t="n">
-        <v>6614626</v>
+        <v>6614604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,12 +2605,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,15 +2637,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114978754</v>
+        <v>113314627</v>
       </c>
       <c r="B22" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,14 +2669,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676201</v>
+        <v>676172</v>
       </c>
       <c r="R22" t="n">
-        <v>6614619</v>
+        <v>6614601</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,12 +2703,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2834,63 +2723,58 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114977437</v>
+        <v>113316500</v>
       </c>
       <c r="B23" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>675968</v>
+        <v>676168</v>
       </c>
       <c r="R23" t="n">
-        <v>6614628</v>
+        <v>6614617</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,12 +2801,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2937,27 +2821,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114977198</v>
+        <v>114976199</v>
       </c>
       <c r="B24" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,35 +2844,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>676004</v>
+        <v>676142</v>
       </c>
       <c r="R24" t="n">
-        <v>6614614</v>
+        <v>6614564</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3052,15 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114976199</v>
+        <v>114978026</v>
       </c>
       <c r="B25" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3089,14 +2963,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkärret, Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676142</v>
+        <v>675976</v>
       </c>
       <c r="R25" t="n">
-        <v>6614564</v>
+        <v>6614671</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3155,15 +3029,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114978291</v>
+        <v>114978658</v>
       </c>
       <c r="B26" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,35 +3040,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676057</v>
+        <v>676170</v>
       </c>
       <c r="R26" t="n">
-        <v>6614574</v>
+        <v>6614608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,27 +3115,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Pöllänen</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114978658</v>
+        <v>114978754</v>
       </c>
       <c r="B27" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3295,14 +3159,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>676170</v>
+        <v>676201</v>
       </c>
       <c r="R27" t="n">
-        <v>6614608</v>
+        <v>6614619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,51 +3225,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114976462</v>
+        <v>114977198</v>
       </c>
       <c r="B28" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>676099</v>
+        <v>676004</v>
       </c>
       <c r="R28" t="n">
-        <v>6614533</v>
+        <v>6614614</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3464,51 +3323,51 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>114977540</v>
+        <v>114977300</v>
       </c>
       <c r="B29" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>675957</v>
+        <v>675966</v>
       </c>
       <c r="R29" t="n">
-        <v>6614653</v>
+        <v>6614654</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3567,15 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>114976438</v>
+        <v>114978278</v>
       </c>
       <c r="B30" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,35 +3437,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676122</v>
+        <v>676070</v>
       </c>
       <c r="R30" t="n">
-        <v>6614523</v>
+        <v>6614606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3670,51 +3529,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>114977093</v>
+        <v>113316046</v>
       </c>
       <c r="B31" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>675999</v>
+        <v>676020</v>
       </c>
       <c r="R31" t="n">
-        <v>6614613</v>
+        <v>6614565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,12 +3595,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3761,27 +3615,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>114978933</v>
+        <v>114976338</v>
       </c>
       <c r="B32" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3789,35 +3638,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långkärret, Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>676142</v>
+        <v>676160</v>
       </c>
       <c r="R32" t="n">
-        <v>6614564</v>
+        <v>6614538</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,15 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>114976338</v>
+        <v>114978283</v>
       </c>
       <c r="B33" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3913,14 +3757,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676160</v>
+        <v>676054</v>
       </c>
       <c r="R33" t="n">
-        <v>6614538</v>
+        <v>6614536</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,68 +3811,58 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>114977300</v>
+        <v>114978291</v>
       </c>
       <c r="B34" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>675966</v>
+        <v>676057</v>
       </c>
       <c r="R34" t="n">
-        <v>6614654</v>
+        <v>6614574</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,27 +3909,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114976365</v>
+        <v>114978809</v>
       </c>
       <c r="B35" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,35 +3932,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>676151</v>
+        <v>676159</v>
       </c>
       <c r="R35" t="n">
-        <v>6614510</v>
+        <v>6614531</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,66 +4007,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>114977763</v>
+        <v>116312903</v>
       </c>
       <c r="B36" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>675950</v>
+        <v>676118</v>
       </c>
       <c r="R36" t="n">
-        <v>6614674</v>
+        <v>6614535</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4261,12 +4084,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4281,27 +4114,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>114978026</v>
+        <v>113279738</v>
       </c>
       <c r="B37" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4309,35 +4137,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>675976</v>
+        <v>676034</v>
       </c>
       <c r="R37" t="n">
-        <v>6614671</v>
+        <v>6614554</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4364,12 +4192,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4384,27 +4212,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>114976226</v>
+        <v>113279813</v>
       </c>
       <c r="B38" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,14 +4256,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långkärret, Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>676142</v>
+        <v>676066</v>
       </c>
       <c r="R38" t="n">
-        <v>6614564</v>
+        <v>6614544</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4467,12 +4290,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,27 +4310,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116312903</v>
+        <v>113279911</v>
       </c>
       <c r="B39" t="n">
-        <v>96715</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,37 +4333,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långkärret (Långkärret), Upl</t>
+          <t>Långkärret, Långkärret, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>676118</v>
+        <v>676137</v>
       </c>
       <c r="R39" t="n">
-        <v>6614535</v>
+        <v>6614516</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4569,22 +4388,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4599,15 +4408,518 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>114976012</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>676142</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6614564</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>114976365</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>676151</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6614510</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>114976438</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>676122</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6614523</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>116291627</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>676113</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6614498</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>116291666</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långkärret, Långkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>676116</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6614496</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
